--- a/sheets/국악이꽃피는나무/검수/뱃노래.xlsx
+++ b/sheets/국악이꽃피는나무/검수/뱃노래.xlsx
@@ -4520,16 +4520,11 @@
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F14" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">▽</t>
-        </is>
-      </c>
+      <c r="F14" s="27"/>
       <c r="G14" s="28"/>
       <c r="H14" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-▽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I14" s="28" t="inlineStr">
@@ -4537,16 +4532,11 @@
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J14" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">▽</t>
-        </is>
-      </c>
+      <c r="J14" s="27"/>
       <c r="K14" s="28"/>
       <c r="L14" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-▽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="M14" s="28" t="inlineStr">
@@ -4554,11 +4544,7 @@
           <t xml:space="preserve">차</t>
         </is>
       </c>
-      <c r="N14" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">▽</t>
-        </is>
-      </c>
+      <c r="N14" s="27"/>
       <c r="O14" s="28"/>
     </row>
   </sheetData>

--- a/sheets/국악이꽃피는나무/검수/뱃노래.xlsx
+++ b/sheets/국악이꽃피는나무/검수/뱃노래.xlsx
@@ -3766,26 +3766,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="50.63" customHeight="true">
+    <row r="2" ht="56.34" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="75.27" customHeight="true">
+    <row r="3" ht="83.81" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="75.27" customHeight="true">
+    <row r="4" ht="83.81" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="75.27" customHeight="true">
+    <row r="5" ht="83.81" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="75.27" customHeight="true">
+    <row r="6" ht="83.81" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="75.27" customHeight="true">
+    <row r="7" ht="83.81" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="75.27" customHeight="true">
+    <row r="8" ht="83.81" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="75.27" customHeight="true">
+    <row r="9" ht="83.81" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="75.27" customHeight="true">
+    <row r="10" ht="83.81" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="O10" s="23"/>
     </row>
-    <row r="11" ht="75.27" customHeight="true">
+    <row r="11" ht="83.81" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="O11" s="24"/>
     </row>
-    <row r="12" ht="75.27" customHeight="true">
+    <row r="12" ht="83.81" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O12" s="22"/>
     </row>
-    <row r="13" ht="75.27" customHeight="true">
+    <row r="13" ht="83.81" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="75.27" customHeight="true">
+    <row r="14" ht="83.81" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="25" t="inlineStr">
         <is>
@@ -4553,6 +4553,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="79"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="71"/>
 </worksheet>
 </file>